--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/IOWA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/IOWA_2021.xlsx
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C177">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C184">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C504">
